--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2933,14 +2933,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.5</v>
+        <v>49.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>55.1</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.3</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3566,11 +3566,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
@@ -3579,13 +3579,13 @@
         <v>55.1</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3598,12 +3598,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3675,67 +3675,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -4103,24 +4103,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4133,14 +4133,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4154,26 +4166,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>55.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4186,24 +4198,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4216,7 +4228,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4233,12 +4245,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4248,12 +4260,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4263,75 +4275,99 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>38 deg</t>
@@ -4385,12 +4421,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4415,7 +4451,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4434,7 +4470,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4448,11 +4484,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
@@ -4461,13 +4497,13 @@
         <v>55.1</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4480,12 +4516,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4527,27 +4563,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4557,67 +4593,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4703,12 +4739,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4733,7 +4769,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4752,7 +4788,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.8</v>
+        <v>35</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4766,11 +4802,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
@@ -4779,13 +4815,13 @@
         <v>55.1</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -4798,12 +4834,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -4845,27 +4881,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -4875,67 +4911,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5104,7 +5140,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -5221,7 +5257,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -5303,24 +5339,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5336,23 +5372,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>694819</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5366,14 +5390,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>41.2</v>
       </c>
       <c r="R17" t="n">
         <v>55.1</v>
@@ -5382,10 +5406,10 @@
         <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5398,24 +5422,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5428,7 +5452,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5445,12 +5469,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5460,12 +5484,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5475,99 +5499,75 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>0.0996</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>25.57</t>
-        </is>
-      </c>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
           <t>38 deg</t>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -8781,14 +8781,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.5</v>
+        <v>49.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>55.1</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -9351,12 +9351,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9400,7 +9400,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.3</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9414,11 +9414,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
@@ -9427,13 +9427,13 @@
         <v>55.1</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9446,12 +9446,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -9493,27 +9493,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9523,67 +9523,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -9951,24 +9951,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -9981,14 +9981,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10002,26 +10014,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>55.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10034,24 +10046,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10064,7 +10076,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10081,12 +10093,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -10096,12 +10108,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10111,75 +10123,99 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>38 deg</t>
@@ -10233,12 +10269,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10263,7 +10299,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10282,7 +10318,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10296,11 +10332,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
@@ -10309,13 +10345,13 @@
         <v>55.1</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10328,12 +10364,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10375,27 +10411,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10405,67 +10441,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -10551,12 +10587,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10581,7 +10617,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -10600,7 +10636,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.8</v>
+        <v>35</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10614,11 +10650,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
@@ -10627,13 +10663,13 @@
         <v>55.1</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -10646,12 +10682,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -10693,27 +10729,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -10723,67 +10759,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -10952,7 +10988,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -11069,7 +11105,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -11151,24 +11187,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -11184,23 +11220,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>694819</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11214,14 +11238,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>41.2</v>
       </c>
       <c r="R17" t="n">
         <v>55.1</v>
@@ -11230,10 +11254,10 @@
         <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11246,24 +11270,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11276,7 +11300,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11293,12 +11317,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11308,12 +11332,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11323,99 +11347,75 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>0.0996</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>25.57</t>
-        </is>
-      </c>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
           <t>38 deg</t>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -848,11 +848,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>57.2</v>
+        <v>56.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -866,23 +878,23 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R2" t="n">
         <v>55.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
         <v>16.6</v>
@@ -893,42 +905,38 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -965,7 +973,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1038,15 +1046,39 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1122,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1130,11 +1162,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1148,23 +1192,23 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>50.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R3" t="n">
         <v>55.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
         <v>63.3</v>
@@ -1175,42 +1219,38 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -1247,7 +1287,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1320,15 +1360,39 @@
           <t>0.1951</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1379,24 +1443,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1404,19 +1468,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1430,26 +1506,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>55.1</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -1457,42 +1533,38 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -1509,12 +1581,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1524,12 +1596,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1539,78 +1611,102 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1661,12 +1757,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1676,7 +1772,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1686,12 +1782,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1710,7 +1806,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.9</v>
+        <v>51.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1724,11 +1820,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q5" t="n">
         <v>18.6</v>
@@ -1737,53 +1833,51 @@
         <v>55.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>48</v>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1803,12 +1897,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1818,82 +1912,82 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -1928,7 +2022,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -1962,16 +2056,56 @@
         </is>
       </c>
       <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1979,24 +2113,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -2004,22 +2138,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2028,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2042,68 +2176,62 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>61.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
         <v>55.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
+        <v>80</v>
+      </c>
+      <c r="U6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="V6" t="n">
         <v>50</v>
       </c>
-      <c r="U6" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>48</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2123,132 +2251,132 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2282,56 +2410,16 @@
         </is>
       </c>
       <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2339,12 +2427,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2364,19 +2452,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2390,26 +2490,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R7" t="n">
         <v>55.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2417,42 +2517,38 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2469,27 +2565,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2499,78 +2595,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2621,12 +2741,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2646,19 +2766,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>50.5</v>
+        <v>48.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2672,26 +2804,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>55.1</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2699,42 +2831,38 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -2751,7 +2879,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2766,12 +2894,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2781,78 +2909,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -2928,19 +3080,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>49.8</v>
+        <v>45.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2954,23 +3118,23 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
         <v>55.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
         <v>13.3</v>
@@ -2981,42 +3145,38 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -3053,7 +3213,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3126,15 +3286,39 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3190,7 +3374,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3210,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3234,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.7</v>
+        <v>45.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3248,7 +3432,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3261,7 +3445,7 @@
         <v>55.1</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3275,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3452,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3503,12 +3683,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3528,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3552,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.9</v>
+        <v>39.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3566,11 +3746,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
@@ -3579,13 +3759,13 @@
         <v>55.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3593,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3645,27 +3821,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3675,67 +3851,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3770,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3821,24 +3997,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3846,19 +4022,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3872,26 +4060,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R12" t="n">
         <v>55.1</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -3899,42 +4087,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -3956,7 +4140,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -3966,12 +4150,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -3981,78 +4165,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4103,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4128,12 +4336,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4152,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.9</v>
+        <v>37.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4166,11 +4374,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
@@ -4179,13 +4387,13 @@
         <v>55.1</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4193,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4245,27 +4449,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4275,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4370,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4421,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4446,22 +4650,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4470,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4484,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R14" t="n">
         <v>55.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4511,39 +4715,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4563,27 +4763,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4593,102 +4793,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4739,24 +4939,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4764,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4774,12 +4974,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4788,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>34.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4802,26 +5002,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
         <v>55.1</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>24.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -4829,42 +5029,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -4881,12 +5077,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4896,12 +5092,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -4911,102 +5107,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5082,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5090,11 +5286,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5108,23 +5316,23 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
         <v>55.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>23.7</v>
@@ -5135,42 +5343,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5207,7 +5411,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5280,15 +5484,39 @@
           <t>0.1042</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5339,24 +5567,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5364,19 +5592,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>33.7</v>
+        <v>32.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5390,26 +5630,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
         <v>55.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5417,42 +5657,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5469,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5484,12 +5720,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5499,78 +5735,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5621,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5646,12 +5906,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5670,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5684,11 +5944,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q18" t="n">
         <v>18.6</v>
@@ -5697,13 +5957,13 @@
         <v>55.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5711,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5763,12 +6019,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5778,12 +6034,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -5793,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -5888,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -5964,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5988,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.9</v>
+        <v>29.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6002,7 +6258,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6015,7 +6271,7 @@
         <v>55.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6029,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6206,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6688,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6696,11 +6948,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>57.2</v>
+        <v>56.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6714,23 +6978,23 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R2" t="n">
         <v>55.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
         <v>16.6</v>
@@ -6741,42 +7005,38 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -6813,7 +7073,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -6886,15 +7146,39 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -6970,7 +7254,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6978,11 +7262,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6996,23 +7292,23 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>50.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R3" t="n">
         <v>55.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
         <v>63.3</v>
@@ -7023,42 +7319,38 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -7095,7 +7387,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -7168,15 +7460,39 @@
           <t>0.1951</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7227,24 +7543,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -7252,19 +7568,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7278,26 +7606,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>55.1</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -7305,42 +7633,38 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -7357,12 +7681,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -7372,12 +7696,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -7387,78 +7711,102 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7509,12 +7857,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7524,7 +7872,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7534,12 +7882,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -7558,7 +7906,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.9</v>
+        <v>51.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7572,11 +7920,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q5" t="n">
         <v>18.6</v>
@@ -7585,53 +7933,51 @@
         <v>55.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>48</v>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7651,12 +7997,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -7666,82 +8012,82 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -7776,7 +8122,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -7810,16 +8156,56 @@
         </is>
       </c>
       <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7827,24 +8213,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -7852,22 +8238,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7876,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7890,68 +8276,62 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>61.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
         <v>55.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
+        <v>80</v>
+      </c>
+      <c r="U6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="V6" t="n">
         <v>50</v>
       </c>
-      <c r="U6" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>48</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7971,132 +8351,132 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8130,56 +8510,16 @@
         </is>
       </c>
       <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8187,12 +8527,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8212,19 +8552,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8238,26 +8590,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R7" t="n">
         <v>55.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8265,42 +8617,38 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8317,27 +8665,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8347,78 +8695,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1565</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8469,12 +8841,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8494,19 +8866,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>50.5</v>
+        <v>48.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8520,26 +8904,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>55.1</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8547,42 +8931,38 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -8599,7 +8979,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -8614,12 +8994,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -8629,78 +9009,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -8776,19 +9180,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>49.8</v>
+        <v>45.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8802,23 +9218,23 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
         <v>55.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
         <v>13.3</v>
@@ -8829,42 +9245,38 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -8901,7 +9313,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -8974,15 +9386,39 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9038,7 +9474,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9058,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9082,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.7</v>
+        <v>45.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9096,7 +9532,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9109,7 +9545,7 @@
         <v>55.1</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -9123,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9300,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9351,12 +9783,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9376,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9400,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.9</v>
+        <v>39.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9414,11 +9846,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
@@ -9427,13 +9859,13 @@
         <v>55.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9441,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9493,27 +9921,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9523,67 +9951,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -9618,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -9669,24 +10097,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -9694,19 +10122,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9720,26 +10160,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R12" t="n">
         <v>55.1</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -9747,42 +10187,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -9804,7 +10240,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -9814,12 +10250,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -9829,78 +10265,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -9951,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9976,12 +10436,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10000,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.9</v>
+        <v>37.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10014,11 +10474,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
@@ -10027,13 +10487,13 @@
         <v>55.1</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10041,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10093,27 +10549,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10123,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10218,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10269,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -10294,22 +10750,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10318,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10332,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R14" t="n">
         <v>55.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10359,39 +10815,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10411,27 +10863,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10441,102 +10893,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -10587,24 +11039,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -10612,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10622,12 +11074,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -10636,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>34.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10650,26 +11102,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
         <v>55.1</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>24.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -10677,42 +11129,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -10729,12 +11177,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -10744,12 +11192,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -10759,102 +11207,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -10930,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10938,11 +11386,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10956,23 +11416,23 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
         <v>55.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>23.7</v>
@@ -10983,42 +11443,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11055,7 +11511,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11128,15 +11584,39 @@
           <t>0.1042</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11187,24 +11667,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -11212,19 +11692,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>33.7</v>
+        <v>32.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11238,26 +11730,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
         <v>55.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11265,42 +11757,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11317,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11332,12 +11820,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11347,78 +11835,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -11469,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11494,12 +12006,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -11518,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11532,11 +12044,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q18" t="n">
         <v>18.6</v>
@@ -11545,13 +12057,13 @@
         <v>55.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -11559,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11611,12 +12119,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -11626,12 +12134,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -11641,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -11736,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -11812,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11836,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.9</v>
+        <v>29.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11850,7 +12358,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11863,7 +12371,7 @@
         <v>55.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -11877,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12054,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>38 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
